--- a/data/trans_orig/IP07C13-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C13-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de estar contento con su forma de ser en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de estar contento/a con su forma de ser en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18706</t>
+          <t>18567</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29463</t>
+          <t>29010</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18769</t>
+          <t>19386</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28898</t>
+          <t>29363</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40219</t>
+          <t>40752</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55944</t>
+          <t>56022</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,23%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14091</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>25266</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12363</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22555</t>
+          <t>21909</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28980</t>
+          <t>28726</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44357</t>
+          <t>43772</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,41%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82347</t>
+          <t>83504</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105644</t>
+          <t>105076</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>114164</t>
+          <t>115217</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137187</t>
+          <t>137271</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>203506</t>
+          <t>203025</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236397</t>
+          <t>235606</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,98%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69462</t>
+          <t>68893</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91473</t>
+          <t>91034</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66471</t>
+          <t>66302</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89469</t>
+          <t>88375</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141863</t>
+          <t>143953</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>174040</t>
+          <t>175697</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>43,24%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>9432</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22204</t>
+          <t>20656</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>5758</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15865</t>
+          <t>16076</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33459</t>
+          <t>33102</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>465</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24138</t>
+          <t>23612</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35644</t>
+          <t>35675</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20883</t>
+          <t>20594</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31552</t>
+          <t>31947</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47684</t>
+          <t>47265</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64772</t>
+          <t>63559</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>62,02%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13596</t>
+          <t>13616</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24887</t>
+          <t>24495</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12638</t>
+          <t>12535</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>23240</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28736</t>
+          <t>29544</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44522</t>
+          <t>45292</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>44,2%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>11471</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133529</t>
+          <t>134832</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>161198</t>
+          <t>163562</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>161906</t>
+          <t>162688</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>189519</t>
+          <t>190414</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>304489</t>
+          <t>303698</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>342651</t>
+          <t>342868</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,39%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>106096</t>
+          <t>103672</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>131644</t>
+          <t>132260</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>99791</t>
+          <t>99166</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>126102</t>
+          <t>125817</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>213939</t>
+          <t>212815</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>251174</t>
+          <t>250509</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13530</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>27814</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22220</t>
+          <t>21170</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>26225</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>45076</t>
+          <t>43856</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,82 +3132,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>4386</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>4460</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>8847</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1245</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>4137</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>4460</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>9023</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de estar contento con su forma de ser en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de estar contento/a con su forma de ser en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25661</t>
+          <t>26756</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37657</t>
+          <t>37726</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19198</t>
+          <t>19546</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30354</t>
+          <t>31165</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49593</t>
+          <t>49427</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65445</t>
+          <t>65916</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,57%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>9156</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20491</t>
+          <t>19910</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>13027</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24536</t>
+          <t>24676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25658</t>
+          <t>25478</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41006</t>
+          <t>40897</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,54%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3482</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7772</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5526</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>660</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97178</t>
+          <t>96202</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120535</t>
+          <t>120492</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>132748</t>
+          <t>131383</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155674</t>
+          <t>155032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>235624</t>
+          <t>235349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>268245</t>
+          <t>269766</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,64%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60403</t>
+          <t>60620</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83223</t>
+          <t>84325</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54787</t>
+          <t>54954</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77056</t>
+          <t>78045</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121695</t>
+          <t>122239</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154083</t>
+          <t>154119</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,36%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23242</t>
+          <t>23333</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5251</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15422</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18183</t>
+          <t>18894</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35211</t>
+          <t>35754</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8254</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>651</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>7969</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33528</t>
+          <t>33524</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45632</t>
+          <t>45395</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32751</t>
+          <t>32628</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44345</t>
+          <t>43759</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69814</t>
+          <t>69417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86701</t>
+          <t>87059</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11273</t>
+          <t>11298</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23186</t>
+          <t>22609</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18395</t>
+          <t>18443</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21955</t>
+          <t>22408</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38565</t>
+          <t>37905</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>724</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>6923</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10240</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>166825</t>
+          <t>165546</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>195940</t>
+          <t>194972</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>194093</t>
+          <t>192686</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>223353</t>
+          <t>220965</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>367535</t>
+          <t>369661</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>410143</t>
+          <t>410537</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>88910</t>
+          <t>89774</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>117377</t>
+          <t>116250</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>83841</t>
+          <t>85188</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>111232</t>
+          <t>112198</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>179967</t>
+          <t>178860</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>219754</t>
+          <t>218754</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>15437</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29881</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>20327</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25944</t>
+          <t>26844</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>45508</t>
+          <t>45731</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>728</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12655</t>
+          <t>12799</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de estar contento con su forma de ser en 2016 (tasa de respuesta: 95,37%)</t>
+          <t>Menores según la frecuencia de estar contento/a con su forma de ser en 2016 (tasa de respuesta: 95,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9566</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18379</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>13089</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22376</t>
+          <t>22445</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24652</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38610</t>
+          <t>38246</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>56,88%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18293</t>
+          <t>19430</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>17146</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19421</t>
+          <t>19455</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33013</t>
+          <t>32923</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,96%</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12898</t>
+          <t>12277</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124981</t>
+          <t>123765</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150232</t>
+          <t>149625</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127823</t>
+          <t>126714</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>152782</t>
+          <t>152213</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>256996</t>
+          <t>257582</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>292952</t>
+          <t>292465</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,96%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74652</t>
+          <t>75431</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99269</t>
+          <t>100898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67742</t>
+          <t>68083</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91587</t>
+          <t>92743</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>151546</t>
+          <t>151744</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>184416</t>
+          <t>185914</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21802</t>
+          <t>22533</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,44 +7573,44 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>14190</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9176</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>21555</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
           <t>3,88%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,96%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>14190</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9101</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>21568</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
           <t>9,12%</t>
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>20655</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38345</t>
+          <t>38214</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>523</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5756</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>785</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7539</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>562</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>563</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35954</t>
+          <t>36380</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49839</t>
+          <t>50063</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44417</t>
+          <t>44207</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57856</t>
+          <t>58092</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84841</t>
+          <t>84447</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103413</t>
+          <t>103697</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,31%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14573</t>
+          <t>14733</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27302</t>
+          <t>26924</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16476</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29545</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34199</t>
+          <t>34446</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53405</t>
+          <t>52533</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10604</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11510</t>
+          <t>11030</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>178355</t>
+          <t>178210</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>208211</t>
+          <t>208269</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>192947</t>
+          <t>193436</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>223949</t>
+          <t>225122</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>380049</t>
+          <t>380194</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>422422</t>
+          <t>424561</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,32%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107989</t>
+          <t>108685</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>136174</t>
+          <t>137970</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>99605</t>
+          <t>101107</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>129345</t>
+          <t>130178</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>217171</t>
+          <t>217140</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>259697</t>
+          <t>260226</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15114</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30508</t>
+          <t>30497</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29194</t>
+          <t>29382</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>32642</t>
+          <t>33016</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53247</t>
+          <t>54780</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>797</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12548</t>
+          <t>12578</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
